--- a/tame_output/ON/bt/strategyON_20240118.xlsx
+++ b/tame_output/ON/bt/strategyON_20240118.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,16 +926,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.9%</t>
+          <t>100.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.0%</t>
+          <t>129.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1845"/>
+  <dimension ref="A1:G1846"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299190136002138</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -43996,6 +43996,29 @@
       </c>
       <c r="G1845" t="n">
         <v>4.466642931731962</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="2" t="n">
+        <v>45308</v>
+      </c>
+      <c r="B1846" t="n">
+        <v>3.294483388684696</v>
+      </c>
+      <c r="C1846" t="n">
+        <v>3.119153558445966</v>
+      </c>
+      <c r="D1846" t="n">
+        <v>1.633042304948723</v>
+      </c>
+      <c r="E1846" t="n">
+        <v>3.772014056111708</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>2.24618173513725</v>
+      </c>
+      <c r="G1846" t="n">
+        <v>4.466862599528316</v>
       </c>
     </row>
   </sheetData>
